--- a/testes/Financeiro/Planilhas_Base/clientes.xlsx
+++ b/testes/Financeiro/Planilhas_Base/clientes.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11415" yWindow="15" windowWidth="17385" windowHeight="14910" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Clientes" sheetId="1" state="visible" r:id="rId1"/>
@@ -48,9 +48,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -419,15 +418,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="43.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="88" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="10.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="30.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="17" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.42578125" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,211 +451,251 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>CNPJ</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Administradores</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>%</t>
+          <t>Data Final</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CLEVER LUIZ SALVADOR</t>
+          <t>FRANCISCO JOSE TOLENTINO BRANDAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RUA MARES DE MONTANHAS, 465 - CONDOMINIO VALE DOS CRISTAIS</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>30104762000107</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>VASCONCELOS &amp; RINALDI ENGENHARIA</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>13</v>
+          <t>RUA CANASTRA, Nº 1.706 - COND. QUINTAS DO MORRO - NOVA LIMA - MG - CEP: 34010-510</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>44474</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>45758</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EDUARDO MORENO MARQUES</t>
+          <t>SERGIO LUCIO PEREIRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALAMEDA SÃO GOTARDO, Nº 268 LOTE 01 QUADRA 16 - VILA ALPINA - NOVA LIMA/MG</t>
-        </is>
-      </c>
+          <t>RUA DA SERENATA Nº225 - VALE DOS CRISTAIS</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>44671</v>
+      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GILMAR ALMEIDA PORTUGAL</t>
+          <t>RONALDO ROLIM DE OLIVEIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUA LÍRIO DO AMANHÃ, L OTE 2 Q 23, n° 85 VALE DOS CRISTAIS</t>
-        </is>
+          <t>ALAMEDA DAS PAINEIRAS Nº 495 - BOSQUE DA RIBEIRA, NOVA LIMA - MG</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>44854</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JOSÉ PAULO DE SOUZA PEIXE</t>
+          <t>FERNANDO HENRIQUE FARIA BARBASSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALAMEDA DA TERNURA 0006, LOTE 369-B, QUADRA ÚNICA - Nº 55 - CONDOMINIO PASARGADA, NOVA LIMA/MG</t>
-        </is>
-      </c>
+          <t>RUA DAS CODORNAS Nº 135 - ESTÂNCIA  SERRANA - NOVA LIMA, MG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>45143</v>
+      </c>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RHAUFED RODRIGUES DOS SANTOS</t>
+          <t>GILMAR ALMEIDA PORTUGAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALAMEDA SÃO GOTARDO Nº 206 L. 3 Q. 16 CONDOMÍNIO VILA ALPINA NOVA LIMA / MG – CEP 34.007-300.</t>
-        </is>
+          <t>RUA LÍRIO DO AMANHÃ, L OTE 2 Q 23, n° 85 VALE DOS CRISTAIS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>45417</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RONALDO ROLIM DE OLIVEIRA</t>
+          <t>RHAUFED RODRIGUES DOS SANTOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ALAMEDA DAS PAINEIRAS Nº 495 - BOSQUE DA RIBEIRA, NOVA LIMA - MG</t>
-        </is>
+          <t>ALAMEDA SÃO GOTARDO Nº 206 L. 3 Q. 16 CONDOMÍNIO VILA ALPINA NOVA LIMA / MG – CEP 34.007-300.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>45448</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JOVERPI LOCADORA E CONSTRUTORA DE IMOVEIS LTDA</t>
+          <t>EDUARDO MORENO MARQUES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AVENIDA JOÃO CESAR DE OLIVEIRA, 2.792, SL 213 - BAIRRO ELDORADO – CONTAGEM/MG. CEP: 32.310-000</t>
+          <t>ALAMEDA SÃO GOTARDO, Nº 268 LOTE 01 QUADRA 16 - VILA ALPINA - NOVA LIMA/MG</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45585</v>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>30104762000107</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VASCONCELOS &amp; RINALDI ENGENHARIA</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>15</v>
+        <v>45509</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FRANCISCO JOSE TOLENTINO BRANDAO</t>
+          <t>JOSE PAULO DE SOUZA PEIXE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RUA CANASTRA, Nº 1.706 - COND. QUINTAS DO MORRO - NOVA LIMA - MG - CEP: 34010-510</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n"/>
+          <t>ALAMEDA DA TERNURA 0006, LOTE 369-B, QUADRA ÚNICA - Nº 55 - CONDOMINIO PASARGADA, NOVA LIMA/MG</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>45509</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MILA MAIA</t>
+          <t>CLEVER LUIZ SALVADOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RUA MARES DAS MONTANHAS, 905 - RES. NASCENTES, VALE DOS CRISTAIS - NOVA LIMA/MG</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>44671</v>
+          <t>RUA MARES DE MONTANHAS, 465 - CONDOMINIO VALE DOS CRISTAIS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>45540</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FERNANDO HENRIQUE FARIA BARBASSA</t>
+          <t>JOVERPI LOCADORA E CONSTRUTORA DE IMOVEIS LTDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RUA DAS CODORNAS Nº 135 - ESTÂNCIA  SERRANA - NOVA LIMA, MG</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>45143</v>
-      </c>
+          <t>AVENIDA JOÃO CESAR DE OLIVEIRA, 2.792, SL 213 - BAIRRO ELDORADO – CONTAGEM/MG. CEP: 32.310-000</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>45585</v>
+      </c>
+      <c r="E11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EDIGAR BATISTA FERREIRA</t>
+          <t>ANA AUGUSTA PIRES COUTINHO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RUA CORONEL JOÃO CAMARGOS, 26 - CENTRO - CONTAGEM/M</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>45112</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LENICE NOGUEIRA</t>
-        </is>
-      </c>
+          <t>RUA NEREIDA, LOTE 17 Q. 39, Nº 409, BAIRRO VALE DO SOL, NOVA LIMA / MG</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45708</v>
+      </c>
+      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SERGIO LUCIO PEREIRA</t>
+          <t>BRUNO SANTANA RINALDI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RUA DA SERENATA Nº225 - VALE DOS CRISTAIS</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
+          <t>RUA ZODIACO,  SALA 7 SANTA LUCIA, BELO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EDIGAR BATISTA FERREIRA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RUA CORONEL JOÃO CAMARGOS, 26 - CENTRO - CONTAGEM/MG</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>45112</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LENICE NOGUEIRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MARCIA UBERENICE NOGUEIRA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ALAMEDA COPAIBEIRA DE MINAS, N.º 1541, LOTE 12 QUADRO 04A CEP 32044-630 ESTÂNCIA DO LAGO, CONTAGEM, MG</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>45828</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MILA MAIA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RUA MARES DAS MONTANHAS, 905 - RES. NASCENTES, VALE DOS CRISTAIS - NOVA LIMA/MG</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>44671</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" s="3" t="n">
+        <v>45693</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
